--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T15:21:05+00:00</t>
+    <t>2025-10-20T17:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-20T17:15:49+00:00</t>
+    <t>2025-10-21T08:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T08:14:34+00:00</t>
+    <t>2025-10-21T15:23:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T15:23:03+00:00</t>
+    <t>2025-10-21T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +105,16 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/OperateurSaisie</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-operateur-saisie</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-data-enterer</t>
-  </si>
-  <si>
-    <t>OperateurSaisie</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-data-enterer</t>
+  </si>
+  <si>
+    <t>FRLMOperateurSaisie</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -123,13 +123,13 @@
     <t>dataEnterer</t>
   </si>
   <si>
-    <t>OperateurSaisie.dateSaisie</t>
+    <t>FRLMOperateurSaisie.dateSaisie</t>
   </si>
   <si>
     <t>dataEnterer.time</t>
   </si>
   <si>
-    <t>OperateurSaisie.operateurSaisie</t>
+    <t>FRLMOperateurSaisie.operateurSaisie</t>
   </si>
   <si>
     <t>dataEnterer.assignedEntity</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T16:49:23+00:00</t>
+    <t>2025-10-21T17:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
+++ b/main/ig/mappingOperateurSaisieCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T17:18:21+00:00</t>
+    <t>2025-10-22T08:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
